--- a/assets/infobasica/planilhas/aula30_nivel2.xlsx
+++ b/assets/infobasica/planilhas/aula30_nivel2.xlsx
@@ -516,7 +516,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dados → Funções nomeadas: crie AREA_RET(largura; comprimento) com a definição =larguracomprimento.</t>
+          <t>Dados → Funções nomeadas: crie AREA_RET(largura; comprimento) com a definição =largura*comprimento.</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
